--- a/Results_experiment/exp_2/preds_1111114442222222.xlsx
+++ b/Results_experiment/exp_2/preds_1111114442222222.xlsx
@@ -1179,7 +1179,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D2">
-        <v>-1.962946891784668</v>
+        <v>-2.314095258712769</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1193,7 +1193,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D3">
-        <v>4.863190650939941</v>
+        <v>1.846703290939331</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1207,7 +1207,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D4">
-        <v>1.774534344673157</v>
+        <v>1.198946595191956</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1221,7 +1221,7 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>0.3300323784351349</v>
+        <v>0.2650763392448425</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1235,7 +1235,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D6">
-        <v>4.237210273742676</v>
+        <v>4.895900726318359</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1249,7 +1249,7 @@
         <v>-1.299999952316284</v>
       </c>
       <c r="D7">
-        <v>5.413665294647217</v>
+        <v>4.177018642425537</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1263,7 +1263,7 @@
         <v>-7</v>
       </c>
       <c r="D8">
-        <v>-1.053833842277527</v>
+        <v>-2.701729297637939</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1277,7 +1277,7 @@
         <v>15.39999961853027</v>
       </c>
       <c r="D9">
-        <v>10.6345272064209</v>
+        <v>10.46494293212891</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1291,7 +1291,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D10">
-        <v>8.03935432434082</v>
+        <v>6.630043983459473</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1305,7 +1305,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D11">
-        <v>-1.02907919883728</v>
+        <v>-0.9374950528144836</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1319,7 +1319,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D12">
-        <v>-1.747002124786377</v>
+        <v>-1.049058198928833</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1333,7 +1333,7 @@
         <v>11.19999980926514</v>
       </c>
       <c r="D13">
-        <v>10.93006324768066</v>
+        <v>9.492239952087402</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1347,7 +1347,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D14">
-        <v>-2.445801019668579</v>
+        <v>-2.72698974609375</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1361,7 +1361,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D15">
-        <v>0.5667374730110168</v>
+        <v>1.263976097106934</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1375,7 +1375,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D16">
-        <v>2.621033430099487</v>
+        <v>2.407355546951294</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1389,7 +1389,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D17">
-        <v>-0.7424734830856323</v>
+        <v>-0.5846001505851746</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1403,7 +1403,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D18">
-        <v>11.03297233581543</v>
+        <v>10.59711074829102</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1417,7 +1417,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D19">
-        <v>3.088854074478149</v>
+        <v>1.459542512893677</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1431,7 +1431,7 @@
         <v>13.10000038146973</v>
       </c>
       <c r="D20">
-        <v>8.172595977783203</v>
+        <v>7.949610710144043</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1445,7 +1445,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D21">
-        <v>3.204093456268311</v>
+        <v>2.491968631744385</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1459,7 +1459,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D22">
-        <v>-0.4659606218338013</v>
+        <v>-0.4456713795661926</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1473,7 +1473,7 @@
         <v>-1</v>
       </c>
       <c r="D23">
-        <v>-0.4291117191314697</v>
+        <v>-0.51016765832901</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1487,7 +1487,7 @@
         <v>11.5</v>
       </c>
       <c r="D24">
-        <v>2.587999582290649</v>
+        <v>4.739522457122803</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1501,7 +1501,7 @@
         <v>-14.5</v>
       </c>
       <c r="D25">
-        <v>-6.897406578063965</v>
+        <v>-5.903574466705322</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1515,7 +1515,7 @@
         <v>1</v>
       </c>
       <c r="D26">
-        <v>2.338960647583008</v>
+        <v>2.844784736633301</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -1529,7 +1529,7 @@
         <v>3.400000095367432</v>
       </c>
       <c r="D27">
-        <v>3.123856782913208</v>
+        <v>2.551834106445312</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -1543,7 +1543,7 @@
         <v>26.89999961853027</v>
       </c>
       <c r="D28">
-        <v>19.77696228027344</v>
+        <v>18.10348320007324</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -1557,7 +1557,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="D29">
-        <v>3.882780790328979</v>
+        <v>4.16132926940918</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -1571,7 +1571,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D30">
-        <v>1.987373232841492</v>
+        <v>2.202948808670044</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -1585,7 +1585,7 @@
         <v>10.5</v>
       </c>
       <c r="D31">
-        <v>3.951564788818359</v>
+        <v>4.247604370117188</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1599,7 +1599,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D32">
-        <v>3.799667835235596</v>
+        <v>2.321346521377563</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -1613,7 +1613,7 @@
         <v>12.10000038146973</v>
       </c>
       <c r="D33">
-        <v>7.868478775024414</v>
+        <v>6.867682933807373</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1627,7 +1627,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D34">
-        <v>3.728946447372437</v>
+        <v>3.479068517684937</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1641,7 +1641,7 @@
         <v>-9.800000190734863</v>
       </c>
       <c r="D35">
-        <v>-2.616574764251709</v>
+        <v>-2.821707963943481</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1655,7 +1655,7 @@
         <v>6.5</v>
       </c>
       <c r="D36">
-        <v>4.058192253112793</v>
+        <v>4.250695705413818</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1669,7 +1669,7 @@
         <v>-4.199999809265137</v>
       </c>
       <c r="D37">
-        <v>-3.270943164825439</v>
+        <v>-3.632386207580566</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1683,7 +1683,7 @@
         <v>9.800000190734863</v>
       </c>
       <c r="D38">
-        <v>7.281834125518799</v>
+        <v>7.500996589660645</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1697,7 +1697,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D39">
-        <v>7.669327259063721</v>
+        <v>10.25509452819824</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1711,7 +1711,7 @@
         <v>5.699999809265137</v>
       </c>
       <c r="D40">
-        <v>3.559355735778809</v>
+        <v>3.411771774291992</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1725,7 +1725,7 @@
         <v>1.5</v>
       </c>
       <c r="D41">
-        <v>4.711760997772217</v>
+        <v>3.818767547607422</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1739,7 +1739,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D42">
-        <v>-1.408349394798279</v>
+        <v>-1.248615503311157</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1753,7 +1753,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D43">
-        <v>-0.2273036241531372</v>
+        <v>-0.1104173064231873</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1767,7 +1767,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D44">
-        <v>1.259902715682983</v>
+        <v>2.796055793762207</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1781,7 +1781,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D45">
-        <v>6.398711681365967</v>
+        <v>5.006655693054199</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1795,7 +1795,7 @@
         <v>3.5</v>
       </c>
       <c r="D46">
-        <v>-0.7401909828186035</v>
+        <v>-0.4913841485977173</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1809,7 +1809,7 @@
         <v>0.5</v>
       </c>
       <c r="D47">
-        <v>0.007906228303909302</v>
+        <v>-0.3575254082679749</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1823,7 +1823,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D48">
-        <v>-0.3655992150306702</v>
+        <v>0.5020396709442139</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1837,7 +1837,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D49">
-        <v>3.314953327178955</v>
+        <v>2.333463668823242</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1851,7 +1851,7 @@
         <v>-14.69999980926514</v>
       </c>
       <c r="D50">
-        <v>-6.913094043731689</v>
+        <v>-7.86060905456543</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -1865,7 +1865,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D51">
-        <v>-3.020224094390869</v>
+        <v>-2.232129335403442</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -1879,7 +1879,7 @@
         <v>-3.200000047683716</v>
       </c>
       <c r="D52">
-        <v>-0.3896649479866028</v>
+        <v>-1.513791084289551</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1893,7 +1893,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D53">
-        <v>2.595926284790039</v>
+        <v>2.722570180892944</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -1907,7 +1907,7 @@
         <v>6.400000095367432</v>
       </c>
       <c r="D54">
-        <v>6.670411109924316</v>
+        <v>5.612537860870361</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -1921,7 +1921,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D55">
-        <v>2.398303985595703</v>
+        <v>2.391887187957764</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -1935,7 +1935,7 @@
         <v>-13.19999980926514</v>
       </c>
       <c r="D56">
-        <v>0.3993769884109497</v>
+        <v>0.3378591537475586</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1949,7 +1949,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D57">
-        <v>2.37479305267334</v>
+        <v>2.660144090652466</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1963,7 +1963,7 @@
         <v>3.200000047683716</v>
       </c>
       <c r="D58">
-        <v>2.369129657745361</v>
+        <v>1.942371606826782</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -1977,7 +1977,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D59">
-        <v>-2.170609474182129</v>
+        <v>-1.994163036346436</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -1991,7 +1991,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D60">
-        <v>-0.5063061714172363</v>
+        <v>1.062451124191284</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2005,7 +2005,7 @@
         <v>-2</v>
       </c>
       <c r="D61">
-        <v>-0.2688922882080078</v>
+        <v>-0.3076531291007996</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2019,7 +2019,7 @@
         <v>-8.199999809265137</v>
       </c>
       <c r="D62">
-        <v>-7.999423503875732</v>
+        <v>-7.092284679412842</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2033,7 +2033,7 @@
         <v>-4.099999904632568</v>
       </c>
       <c r="D63">
-        <v>-2.064026594161987</v>
+        <v>-1.686241388320923</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2047,7 +2047,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D64">
-        <v>-1.373534560203552</v>
+        <v>-0.8616721034049988</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2061,7 +2061,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D65">
-        <v>2.530938625335693</v>
+        <v>3.353874683380127</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2075,7 +2075,7 @@
         <v>-3.5</v>
       </c>
       <c r="D66">
-        <v>3.39958667755127</v>
+        <v>2.733855247497559</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2089,7 +2089,7 @@
         <v>-4.900000095367432</v>
       </c>
       <c r="D67">
-        <v>-0.3406015634536743</v>
+        <v>-1.928936958312988</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2103,7 +2103,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D68">
-        <v>2.476935863494873</v>
+        <v>1.714396476745605</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2117,7 +2117,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D69">
-        <v>-0.3790665864944458</v>
+        <v>-0.394396960735321</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2131,7 +2131,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D70">
-        <v>1.530680537223816</v>
+        <v>2.247397184371948</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2145,7 +2145,7 @@
         <v>5</v>
       </c>
       <c r="D71">
-        <v>-0.3272209167480469</v>
+        <v>0.1862984597682953</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2159,7 +2159,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D72">
-        <v>4.439712047576904</v>
+        <v>3.798979759216309</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2173,7 +2173,7 @@
         <v>3.900000095367432</v>
       </c>
       <c r="D73">
-        <v>5.084602355957031</v>
+        <v>3.346250772476196</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2187,7 +2187,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D74">
-        <v>-1.227905988693237</v>
+        <v>-1.190613985061646</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2201,7 +2201,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D75">
-        <v>-0.7462434768676758</v>
+        <v>-1.318079471588135</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2215,7 +2215,7 @@
         <v>8.800000190734863</v>
       </c>
       <c r="D76">
-        <v>7.921314239501953</v>
+        <v>6.716753005981445</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2229,7 +2229,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D77">
-        <v>4.452047348022461</v>
+        <v>3.54278826713562</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2243,7 +2243,7 @@
         <v>3.5</v>
       </c>
       <c r="D78">
-        <v>-1.739263534545898</v>
+        <v>-1.42596697807312</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2257,7 +2257,7 @@
         <v>-5.599999904632568</v>
       </c>
       <c r="D79">
-        <v>0.02091789245605469</v>
+        <v>0.5947287678718567</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2271,7 +2271,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D80">
-        <v>2.086356401443481</v>
+        <v>2.28851056098938</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2285,7 +2285,7 @@
         <v>-9.100000381469727</v>
       </c>
       <c r="D81">
-        <v>-2.622576713562012</v>
+        <v>-6.633333683013916</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2299,7 +2299,7 @@
         <v>12.39999961853027</v>
       </c>
       <c r="D82">
-        <v>5.390054225921631</v>
+        <v>4.98581600189209</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -2313,7 +2313,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D83">
-        <v>-0.5605658292770386</v>
+        <v>-0.3632526993751526</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -2327,7 +2327,7 @@
         <v>-9.199999809265137</v>
       </c>
       <c r="D84">
-        <v>-1.276639938354492</v>
+        <v>-2.630057096481323</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -2341,7 +2341,7 @@
         <v>8</v>
       </c>
       <c r="D85">
-        <v>3.909318208694458</v>
+        <v>2.954532384872437</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -2355,7 +2355,7 @@
         <v>-5.800000190734863</v>
       </c>
       <c r="D86">
-        <v>-0.5353655815124512</v>
+        <v>-0.5751408934593201</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -2369,7 +2369,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D87">
-        <v>0.1580387949943542</v>
+        <v>0.1609160602092743</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -2383,7 +2383,7 @@
         <v>9.100000381469727</v>
       </c>
       <c r="D88">
-        <v>6.472665786743164</v>
+        <v>4.794275283813477</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -2397,7 +2397,7 @@
         <v>2.400000095367432</v>
       </c>
       <c r="D89">
-        <v>1.962152719497681</v>
+        <v>1.607056140899658</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -2411,7 +2411,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D90">
-        <v>-1.295751214027405</v>
+        <v>-1.554030895233154</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -2425,7 +2425,7 @@
         <v>13.69999980926514</v>
       </c>
       <c r="D91">
-        <v>13.26403617858887</v>
+        <v>11.38808441162109</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -2439,7 +2439,7 @@
         <v>-0.5</v>
       </c>
       <c r="D92">
-        <v>-3.506698131561279</v>
+        <v>-4.499814033508301</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -2453,7 +2453,7 @@
         <v>4</v>
       </c>
       <c r="D93">
-        <v>6.457139492034912</v>
+        <v>5.513479232788086</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -2467,7 +2467,7 @@
         <v>-1.100000023841858</v>
       </c>
       <c r="D94">
-        <v>0.417489767074585</v>
+        <v>-0.06893998384475708</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -2481,7 +2481,7 @@
         <v>-3.900000095367432</v>
       </c>
       <c r="D95">
-        <v>-1.49281632900238</v>
+        <v>-2.211002826690674</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -2495,7 +2495,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D96">
-        <v>0.3864878416061401</v>
+        <v>0.4354008436203003</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -2509,7 +2509,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D97">
-        <v>6.8327317237854</v>
+        <v>6.130935668945312</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -2523,7 +2523,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D98">
-        <v>7.743686199188232</v>
+        <v>7.392169952392578</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -2537,7 +2537,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D99">
-        <v>0.7472286224365234</v>
+        <v>0.1445898413658142</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -2551,7 +2551,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D100">
-        <v>-2.416176319122314</v>
+        <v>-2.603277444839478</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -2565,7 +2565,7 @@
         <v>4.5</v>
       </c>
       <c r="D101">
-        <v>3.958477020263672</v>
+        <v>4.218848705291748</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -2579,7 +2579,7 @@
         <v>0.4000000059604645</v>
       </c>
       <c r="D102">
-        <v>2.398423433303833</v>
+        <v>2.465450763702393</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -2593,7 +2593,7 @@
         <v>2.200000047683716</v>
       </c>
       <c r="D103">
-        <v>1.876455664634705</v>
+        <v>1.590954065322876</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -2607,7 +2607,7 @@
         <v>10.5</v>
       </c>
       <c r="D104">
-        <v>6.278459072113037</v>
+        <v>5.246686935424805</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -2621,7 +2621,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D105">
-        <v>1.983884453773499</v>
+        <v>1.263530969619751</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -2635,7 +2635,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D106">
-        <v>-0.3059933185577393</v>
+        <v>-0.3217702507972717</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -2649,7 +2649,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D107">
-        <v>9.812173843383789</v>
+        <v>9.814469337463379</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -2663,7 +2663,7 @@
         <v>7.699999809265137</v>
       </c>
       <c r="D108">
-        <v>5.907234668731689</v>
+        <v>5.404590606689453</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -2677,7 +2677,7 @@
         <v>11.80000019073486</v>
       </c>
       <c r="D109">
-        <v>8.812423706054688</v>
+        <v>8.679227828979492</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -2691,7 +2691,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D110">
-        <v>6.738963603973389</v>
+        <v>5.420748710632324</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -2705,7 +2705,7 @@
         <v>-8.300000190734863</v>
       </c>
       <c r="D111">
-        <v>-6.050275325775146</v>
+        <v>-6.531278133392334</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -2719,7 +2719,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D112">
-        <v>-0.4717217087745667</v>
+        <v>-1.746503353118896</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -2733,7 +2733,7 @@
         <v>-5.400000095367432</v>
       </c>
       <c r="D113">
-        <v>-2.402519702911377</v>
+        <v>-2.52540135383606</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -2747,7 +2747,7 @@
         <v>-1</v>
       </c>
       <c r="D114">
-        <v>-1.00188159942627</v>
+        <v>-1.36334228515625</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -2761,7 +2761,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D115">
-        <v>2.106845378875732</v>
+        <v>1.455025434494019</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -2775,7 +2775,7 @@
         <v>-20.29999923706055</v>
       </c>
       <c r="D116">
-        <v>-13.27755546569824</v>
+        <v>-14.31048393249512</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -2789,7 +2789,7 @@
         <v>-5.599999904632568</v>
       </c>
       <c r="D117">
-        <v>-0.4498775601387024</v>
+        <v>-0.5486322641372681</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -2803,7 +2803,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D118">
-        <v>0.3936864733695984</v>
+        <v>-1.336712121963501</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -2817,7 +2817,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D119">
-        <v>3.869757175445557</v>
+        <v>2.833466768264771</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -2831,7 +2831,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D120">
-        <v>-2.562759160995483</v>
+        <v>-2.430771827697754</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -2845,7 +2845,7 @@
         <v>-0.1000000014901161</v>
       </c>
       <c r="D121">
-        <v>-0.699866771697998</v>
+        <v>-0.4508625268936157</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -2859,7 +2859,7 @@
         <v>-20.10000038146973</v>
       </c>
       <c r="D122">
-        <v>0.9742422103881836</v>
+        <v>1.100194334983826</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -2873,7 +2873,7 @@
         <v>6.5</v>
       </c>
       <c r="D123">
-        <v>7.53925085067749</v>
+        <v>7.468438148498535</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -2887,7 +2887,7 @@
         <v>1.100000023841858</v>
       </c>
       <c r="D124">
-        <v>0.3292862176895142</v>
+        <v>0.8609318733215332</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -2901,7 +2901,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D125">
-        <v>-1.548771619796753</v>
+        <v>-1.701384544372559</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -2915,7 +2915,7 @@
         <v>-2.700000047683716</v>
       </c>
       <c r="D126">
-        <v>-1.281277537345886</v>
+        <v>-1.452752590179443</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -2929,7 +2929,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D127">
-        <v>4.228474140167236</v>
+        <v>3.58762526512146</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -2943,7 +2943,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D128">
-        <v>1.630869388580322</v>
+        <v>2.860549926757812</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -2957,7 +2957,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D129">
-        <v>5.110677242279053</v>
+        <v>3.58116626739502</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -2971,7 +2971,7 @@
         <v>-0.5</v>
       </c>
       <c r="D130">
-        <v>-2.119370460510254</v>
+        <v>-2.528657197952271</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -2985,7 +2985,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D131">
-        <v>3.083498001098633</v>
+        <v>2.548685550689697</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -2999,7 +2999,7 @@
         <v>-2.5</v>
       </c>
       <c r="D132">
-        <v>-0.590890645980835</v>
+        <v>-0.4785670638084412</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3013,7 +3013,7 @@
         <v>24.89999961853027</v>
       </c>
       <c r="D133">
-        <v>20.5940990447998</v>
+        <v>20.12399482727051</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3027,7 +3027,7 @@
         <v>0.5</v>
       </c>
       <c r="D134">
-        <v>2.372066974639893</v>
+        <v>2.726776123046875</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3041,7 +3041,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D135">
-        <v>5.054329395294189</v>
+        <v>4.559924125671387</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3055,7 +3055,7 @@
         <v>18.70000076293945</v>
       </c>
       <c r="D136">
-        <v>12.49137878417969</v>
+        <v>12.11075878143311</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3069,7 +3069,7 @@
         <v>-5.199999809265137</v>
       </c>
       <c r="D137">
-        <v>-0.5469439029693604</v>
+        <v>-0.6226473450660706</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3083,7 +3083,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="D138">
-        <v>5.872381687164307</v>
+        <v>5.107747077941895</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3097,7 +3097,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D139">
-        <v>-9.326610565185547</v>
+        <v>-7.29438304901123</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3111,7 +3111,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D140">
-        <v>1.759859919548035</v>
+        <v>1.22042441368103</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3125,7 +3125,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D141">
-        <v>7.28978967666626</v>
+        <v>7.134767055511475</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3139,7 +3139,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="D142">
-        <v>-0.1788735389709473</v>
+        <v>-0.1661136150360107</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3153,7 +3153,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D143">
-        <v>5.150169849395752</v>
+        <v>6.592833518981934</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3167,7 +3167,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D144">
-        <v>0.09550809860229492</v>
+        <v>-0.04501768946647644</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3181,7 +3181,7 @@
         <v>-2.5</v>
       </c>
       <c r="D145">
-        <v>-1.073605537414551</v>
+        <v>-1.269388914108276</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3195,7 +3195,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D146">
-        <v>7.232942581176758</v>
+        <v>7.172366619110107</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3209,7 +3209,7 @@
         <v>13.5</v>
       </c>
       <c r="D147">
-        <v>11.6575984954834</v>
+        <v>10.52802658081055</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3223,7 +3223,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D148">
-        <v>-3.677588939666748</v>
+        <v>-1.21155047416687</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3237,7 +3237,7 @@
         <v>-2.900000095367432</v>
       </c>
       <c r="D149">
-        <v>2.236882209777832</v>
+        <v>0.5195949673652649</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3251,7 +3251,7 @@
         <v>14.10000038146973</v>
       </c>
       <c r="D150">
-        <v>8.959455490112305</v>
+        <v>8.432455062866211</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3265,7 +3265,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D151">
-        <v>4.974316120147705</v>
+        <v>4.341699123382568</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3279,7 +3279,7 @@
         <v>1.399999976158142</v>
       </c>
       <c r="D152">
-        <v>0.2880113124847412</v>
+        <v>0.1128944754600525</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3293,7 +3293,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D153">
-        <v>6.118834018707275</v>
+        <v>6.724734306335449</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3307,7 +3307,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D154">
-        <v>-0.9359050989151001</v>
+        <v>-0.8677995800971985</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3321,7 +3321,7 @@
         <v>-1.5</v>
       </c>
       <c r="D155">
-        <v>-1.773042440414429</v>
+        <v>-1.818569898605347</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -3335,7 +3335,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D156">
-        <v>2.362513303756714</v>
+        <v>2.442479610443115</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -3349,7 +3349,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D157">
-        <v>-1.667387723922729</v>
+        <v>-1.589546680450439</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -3363,7 +3363,7 @@
         <v>9</v>
       </c>
       <c r="D158">
-        <v>-0.3754684925079346</v>
+        <v>2.323975801467896</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -3377,7 +3377,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D159">
-        <v>-0.6810221672058105</v>
+        <v>-1.639852523803711</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -3391,7 +3391,7 @@
         <v>1</v>
       </c>
       <c r="D160">
-        <v>-2.269343376159668</v>
+        <v>-1.11447286605835</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -3405,7 +3405,7 @@
         <v>8</v>
       </c>
       <c r="D161">
-        <v>9.912721633911133</v>
+        <v>10.82997703552246</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -3419,7 +3419,7 @@
         <v>3.799999952316284</v>
       </c>
       <c r="D162">
-        <v>3.203100681304932</v>
+        <v>3.430342674255371</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -3433,7 +3433,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D163">
-        <v>-0.5542879104614258</v>
+        <v>-0.9389486908912659</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -3447,7 +3447,7 @@
         <v>-0.5</v>
       </c>
       <c r="D164">
-        <v>-1.191657185554504</v>
+        <v>-1.106997013092041</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -3461,7 +3461,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D165">
-        <v>1.778532385826111</v>
+        <v>-0.0857740044593811</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -3475,7 +3475,7 @@
         <v>-4.5</v>
       </c>
       <c r="D166">
-        <v>-1.951743602752686</v>
+        <v>-2.571767568588257</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -3489,7 +3489,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D167">
-        <v>2.641780138015747</v>
+        <v>3.171196699142456</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -3503,7 +3503,7 @@
         <v>5.099999904632568</v>
       </c>
       <c r="D168">
-        <v>8.785575866699219</v>
+        <v>6.709434986114502</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -3517,7 +3517,7 @@
         <v>-1</v>
       </c>
       <c r="D169">
-        <v>1.076827883720398</v>
+        <v>0.4762336611747742</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -3531,7 +3531,7 @@
         <v>1.5</v>
       </c>
       <c r="D170">
-        <v>0.2719107270240784</v>
+        <v>0.4151305556297302</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -3545,7 +3545,7 @@
         <v>5.400000095367432</v>
       </c>
       <c r="D171">
-        <v>6.599812030792236</v>
+        <v>6.440659523010254</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -3559,7 +3559,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D172">
-        <v>2.426688671112061</v>
+        <v>-1.188405513763428</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -3573,7 +3573,7 @@
         <v>10.5</v>
       </c>
       <c r="D173">
-        <v>9.247743606567383</v>
+        <v>8.896841049194336</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -3587,7 +3587,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D174">
-        <v>-0.4102841019630432</v>
+        <v>-1.163816213607788</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -3601,7 +3601,7 @@
         <v>12.19999980926514</v>
       </c>
       <c r="D175">
-        <v>5.252611637115479</v>
+        <v>5.820836544036865</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -3615,7 +3615,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D176">
-        <v>2.334298372268677</v>
+        <v>2.640094518661499</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -3629,7 +3629,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D177">
-        <v>-0.7358245849609375</v>
+        <v>-1.098840951919556</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -3643,7 +3643,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D178">
-        <v>6.001997947692871</v>
+        <v>5.679192543029785</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -3657,7 +3657,7 @@
         <v>-10.30000019073486</v>
       </c>
       <c r="D179">
-        <v>-1.469372749328613</v>
+        <v>-2.396359205245972</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -3671,7 +3671,7 @@
         <v>7</v>
       </c>
       <c r="D180">
-        <v>4.498019695281982</v>
+        <v>3.247655391693115</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -3685,7 +3685,7 @@
         <v>0.1000000014901161</v>
       </c>
       <c r="D181">
-        <v>-0.04543018341064453</v>
+        <v>-0.2158759236335754</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -3699,7 +3699,7 @@
         <v>-2</v>
       </c>
       <c r="D182">
-        <v>-1.667688846588135</v>
+        <v>-0.9261900782585144</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -3713,7 +3713,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D183">
-        <v>4.947494506835938</v>
+        <v>4.983063697814941</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -3727,7 +3727,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D184">
-        <v>-7.442311763763428</v>
+        <v>-6.207640647888184</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -3741,7 +3741,7 @@
         <v>-3</v>
       </c>
       <c r="D185">
-        <v>-2.060981273651123</v>
+        <v>-2.580733776092529</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -3755,7 +3755,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D186">
-        <v>2.643248558044434</v>
+        <v>0.8890703916549683</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -3769,7 +3769,7 @@
         <v>7.199999809265137</v>
       </c>
       <c r="D187">
-        <v>7.416752815246582</v>
+        <v>6.369892120361328</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -3783,7 +3783,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D188">
-        <v>2.39398193359375</v>
+        <v>1.754244565963745</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -3797,7 +3797,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D189">
-        <v>3.012184858322144</v>
+        <v>2.406307697296143</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -3811,7 +3811,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D190">
-        <v>0.09683233499526978</v>
+        <v>1.189615488052368</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -3825,7 +3825,7 @@
         <v>1.5</v>
       </c>
       <c r="D191">
-        <v>3.375443935394287</v>
+        <v>0.5546900033950806</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -3839,7 +3839,7 @@
         <v>1</v>
       </c>
       <c r="D192">
-        <v>1.747097134590149</v>
+        <v>2.404102087020874</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -3853,7 +3853,7 @@
         <v>6.099999904632568</v>
       </c>
       <c r="D193">
-        <v>4.642797470092773</v>
+        <v>4.758026123046875</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -3867,7 +3867,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D194">
-        <v>10.07748222351074</v>
+        <v>9.381166458129883</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -3881,7 +3881,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D195">
-        <v>6.248799324035645</v>
+        <v>5.695182800292969</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -3895,7 +3895,7 @@
         <v>4</v>
       </c>
       <c r="D196">
-        <v>1.036481380462646</v>
+        <v>0.2035025656223297</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -3909,7 +3909,7 @@
         <v>7.400000095367432</v>
       </c>
       <c r="D197">
-        <v>5.916083812713623</v>
+        <v>4.911197662353516</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -3923,7 +3923,7 @@
         <v>2.5</v>
       </c>
       <c r="D198">
-        <v>-0.5081213712692261</v>
+        <v>-0.2000591158866882</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -3937,7 +3937,7 @@
         <v>0.2000000029802322</v>
       </c>
       <c r="D199">
-        <v>5.799301624298096</v>
+        <v>5.138924598693848</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -3951,7 +3951,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D200">
-        <v>3.06029748916626</v>
+        <v>2.432459354400635</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -3965,7 +3965,7 @@
         <v>-8.5</v>
       </c>
       <c r="D201">
-        <v>-1.948958158493042</v>
+        <v>-0.9385666251182556</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -3979,7 +3979,7 @@
         <v>9.699999809265137</v>
       </c>
       <c r="D202">
-        <v>5.989904880523682</v>
+        <v>4.41082763671875</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -3993,7 +3993,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D203">
-        <v>-3.605300903320312</v>
+        <v>-4.205452442169189</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4007,7 +4007,7 @@
         <v>-1.5</v>
       </c>
       <c r="D204">
-        <v>1.024143218994141</v>
+        <v>1.505499362945557</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4021,7 +4021,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D205">
-        <v>11.89904594421387</v>
+        <v>11.48840236663818</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4035,7 +4035,7 @@
         <v>2.099999904632568</v>
       </c>
       <c r="D206">
-        <v>2.602130889892578</v>
+        <v>3.815749645233154</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4049,7 +4049,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D207">
-        <v>0.6625725030899048</v>
+        <v>3.016390323638916</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4063,7 +4063,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D208">
-        <v>-0.7315423488616943</v>
+        <v>-1.870980262756348</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4077,7 +4077,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D209">
-        <v>-1.059654712677002</v>
+        <v>-2.027524948120117</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4091,7 +4091,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D210">
-        <v>-0.1632229089736938</v>
+        <v>-0.2643897533416748</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4105,7 +4105,7 @@
         <v>8.699999809265137</v>
       </c>
       <c r="D211">
-        <v>5.770153999328613</v>
+        <v>6.427732944488525</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4119,7 +4119,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D212">
-        <v>4.181606769561768</v>
+        <v>5.977824687957764</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4133,7 +4133,7 @@
         <v>1.5</v>
       </c>
       <c r="D213">
-        <v>3.890896320343018</v>
+        <v>2.701720714569092</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4147,7 +4147,7 @@
         <v>5.800000190734863</v>
       </c>
       <c r="D214">
-        <v>8.795974731445312</v>
+        <v>9.689720153808594</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4161,7 +4161,7 @@
         <v>-6.900000095367432</v>
       </c>
       <c r="D215">
-        <v>-2.589202404022217</v>
+        <v>-0.6281954646110535</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4175,7 +4175,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D216">
-        <v>3.448913097381592</v>
+        <v>4.476847648620605</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4189,7 +4189,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D217">
-        <v>-0.891292929649353</v>
+        <v>-1.6827232837677</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4203,7 +4203,7 @@
         <v>7.800000190734863</v>
       </c>
       <c r="D218">
-        <v>8.440863609313965</v>
+        <v>8.609004974365234</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4217,7 +4217,7 @@
         <v>-4.5</v>
       </c>
       <c r="D219">
-        <v>-4.444778442382812</v>
+        <v>-4.718782424926758</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4231,7 +4231,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D220">
-        <v>5.132145881652832</v>
+        <v>1.391896724700928</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4245,7 +4245,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="D221">
-        <v>6.22036600112915</v>
+        <v>5.932474136352539</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4259,7 +4259,7 @@
         <v>13.69999980926514</v>
       </c>
       <c r="D222">
-        <v>8.943735122680664</v>
+        <v>9.478337287902832</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4273,7 +4273,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D223">
-        <v>-0.5432201623916626</v>
+        <v>-0.3229176998138428</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4287,7 +4287,7 @@
         <v>-7.599999904632568</v>
       </c>
       <c r="D224">
-        <v>-3.347245454788208</v>
+        <v>-3.796586990356445</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4301,7 +4301,7 @@
         <v>-6.300000190734863</v>
       </c>
       <c r="D225">
-        <v>-2.905797958374023</v>
+        <v>-2.849964380264282</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4315,7 +4315,7 @@
         <v>-3</v>
       </c>
       <c r="D226">
-        <v>-1.813219308853149</v>
+        <v>-1.851151943206787</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4329,7 +4329,7 @@
         <v>-1</v>
       </c>
       <c r="D227">
-        <v>-0.7373596429824829</v>
+        <v>-0.7879839539527893</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -4343,7 +4343,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D228">
-        <v>-0.8630988597869873</v>
+        <v>-0.878451406955719</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -4357,7 +4357,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D229">
-        <v>7.828502178192139</v>
+        <v>6.516541481018066</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -4371,7 +4371,7 @@
         <v>10.69999980926514</v>
       </c>
       <c r="D230">
-        <v>3.485569715499878</v>
+        <v>2.896785736083984</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -4385,7 +4385,7 @@
         <v>-1.399999976158142</v>
       </c>
       <c r="D231">
-        <v>0.6176520586013794</v>
+        <v>1.092337131500244</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -4399,7 +4399,7 @@
         <v>4.800000190734863</v>
       </c>
       <c r="D232">
-        <v>8.526426315307617</v>
+        <v>8.751376152038574</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -4413,7 +4413,7 @@
         <v>-11.10000038146973</v>
       </c>
       <c r="D233">
-        <v>-1.563236236572266</v>
+        <v>-2.103486776351929</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -4427,7 +4427,7 @@
         <v>-2.599999904632568</v>
       </c>
       <c r="D234">
-        <v>-1.957487344741821</v>
+        <v>-2.69728946685791</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -4441,7 +4441,7 @@
         <v>7.900000095367432</v>
       </c>
       <c r="D235">
-        <v>4.544405937194824</v>
+        <v>2.997944831848145</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -4455,7 +4455,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D236">
-        <v>4.532809734344482</v>
+        <v>4.55677318572998</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -4469,7 +4469,7 @@
         <v>1.799999952316284</v>
       </c>
       <c r="D237">
-        <v>-0.3381400108337402</v>
+        <v>-1.232161521911621</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -4483,7 +4483,7 @@
         <v>-3.700000047683716</v>
       </c>
       <c r="D238">
-        <v>-1.92504358291626</v>
+        <v>-2.43739652633667</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -4497,7 +4497,7 @@
         <v>3.5</v>
       </c>
       <c r="D239">
-        <v>4.482663154602051</v>
+        <v>3.249396324157715</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -4511,7 +4511,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D240">
-        <v>1.463274359703064</v>
+        <v>1.115998029708862</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -4525,7 +4525,7 @@
         <v>-5.599999904632568</v>
       </c>
       <c r="D241">
-        <v>-0.576265811920166</v>
+        <v>-0.4664691090583801</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -4539,7 +4539,7 @@
         <v>-2.099999904632568</v>
       </c>
       <c r="D242">
-        <v>0.3386901319026947</v>
+        <v>-0.2963940501213074</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -4553,7 +4553,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D243">
-        <v>-1.191059827804565</v>
+        <v>-0.9474254250526428</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -4567,7 +4567,7 @@
         <v>5</v>
       </c>
       <c r="D244">
-        <v>6.242135524749756</v>
+        <v>6.00163459777832</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -4581,7 +4581,7 @@
         <v>15.89999961853027</v>
       </c>
       <c r="D245">
-        <v>12.04235076904297</v>
+        <v>11.06872367858887</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -4595,7 +4595,7 @@
         <v>5.300000190734863</v>
       </c>
       <c r="D246">
-        <v>6.836148262023926</v>
+        <v>6.593874931335449</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -4609,7 +4609,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D247">
-        <v>-1.343999743461609</v>
+        <v>-1.119870901107788</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -4623,7 +4623,7 @@
         <v>9.399999618530273</v>
       </c>
       <c r="D248">
-        <v>5.530375480651855</v>
+        <v>5.81992244720459</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -4637,7 +4637,7 @@
         <v>-6.5</v>
       </c>
       <c r="D249">
-        <v>-2.042633056640625</v>
+        <v>-2.172957897186279</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -4651,7 +4651,7 @@
         <v>-0.6000000238418579</v>
       </c>
       <c r="D250">
-        <v>0.2263537049293518</v>
+        <v>-0.06235316395759583</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -4665,7 +4665,7 @@
         <v>-2.5</v>
       </c>
       <c r="D251">
-        <v>-0.6734046936035156</v>
+        <v>-0.4990231990814209</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -4679,7 +4679,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D252">
-        <v>-1.42732036113739</v>
+        <v>-0.4326735138893127</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -4693,7 +4693,7 @@
         <v>8.600000381469727</v>
       </c>
       <c r="D253">
-        <v>2.534915924072266</v>
+        <v>2.876579284667969</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -4707,7 +4707,7 @@
         <v>7</v>
       </c>
       <c r="D254">
-        <v>4.066611289978027</v>
+        <v>4.099274158477783</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -4721,7 +4721,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D255">
-        <v>-1.964475154876709</v>
+        <v>-2.45383358001709</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -4735,7 +4735,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D256">
-        <v>2.861515760421753</v>
+        <v>2.216624975204468</v>
       </c>
     </row>
     <row r="257" spans="1:4">
@@ -4749,7 +4749,7 @@
         <v>-4.400000095367432</v>
       </c>
       <c r="D257">
-        <v>1.215426445007324</v>
+        <v>1.858668088912964</v>
       </c>
     </row>
     <row r="258" spans="1:4">
@@ -4763,7 +4763,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D258">
-        <v>-0.6455426216125488</v>
+        <v>-0.5222870707511902</v>
       </c>
     </row>
     <row r="259" spans="1:4">
@@ -4777,7 +4777,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D259">
-        <v>-0.4128791689872742</v>
+        <v>-0.4821105599403381</v>
       </c>
     </row>
     <row r="260" spans="1:4">
@@ -4791,7 +4791,7 @@
         <v>-0.800000011920929</v>
       </c>
       <c r="D260">
-        <v>0.1392565965652466</v>
+        <v>0.1650739312171936</v>
       </c>
     </row>
     <row r="261" spans="1:4">
@@ -4805,7 +4805,7 @@
         <v>9.5</v>
       </c>
       <c r="D261">
-        <v>5.810131549835205</v>
+        <v>4.490925312042236</v>
       </c>
     </row>
     <row r="262" spans="1:4">
@@ -4819,7 +4819,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D262">
-        <v>-2.556115627288818</v>
+        <v>-2.177154541015625</v>
       </c>
     </row>
     <row r="263" spans="1:4">
@@ -4833,7 +4833,7 @@
         <v>-3.400000095367432</v>
       </c>
       <c r="D263">
-        <v>0.5148508548736572</v>
+        <v>0.0186704695224762</v>
       </c>
     </row>
     <row r="264" spans="1:4">
@@ -4847,7 +4847,7 @@
         <v>1.299999952316284</v>
       </c>
       <c r="D264">
-        <v>5.595947742462158</v>
+        <v>4.737468719482422</v>
       </c>
     </row>
     <row r="265" spans="1:4">
@@ -4861,7 +4861,7 @@
         <v>-5.099999904632568</v>
       </c>
       <c r="D265">
-        <v>0.7373471260070801</v>
+        <v>-0.5429409146308899</v>
       </c>
     </row>
     <row r="266" spans="1:4">
@@ -4875,7 +4875,7 @@
         <v>6.599999904632568</v>
       </c>
       <c r="D266">
-        <v>5.16178560256958</v>
+        <v>3.938886165618896</v>
       </c>
     </row>
     <row r="267" spans="1:4">
@@ -4889,7 +4889,7 @@
         <v>-0.300000011920929</v>
       </c>
       <c r="D267">
-        <v>-0.8304222822189331</v>
+        <v>-2.140662670135498</v>
       </c>
     </row>
     <row r="268" spans="1:4">
@@ -4903,7 +4903,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D268">
-        <v>-1.729837417602539</v>
+        <v>-2.31912088394165</v>
       </c>
     </row>
     <row r="269" spans="1:4">
@@ -4917,7 +4917,7 @@
         <v>8.899999618530273</v>
       </c>
       <c r="D269">
-        <v>9.514944076538086</v>
+        <v>7.776410102844238</v>
       </c>
     </row>
     <row r="270" spans="1:4">
@@ -4931,7 +4931,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D270">
-        <v>-0.05857312679290771</v>
+        <v>-0.7677037119865417</v>
       </c>
     </row>
     <row r="271" spans="1:4">
@@ -4945,7 +4945,7 @@
         <v>2.799999952316284</v>
       </c>
       <c r="D271">
-        <v>1.391111135482788</v>
+        <v>0.9608326554298401</v>
       </c>
     </row>
     <row r="272" spans="1:4">
@@ -4959,7 +4959,7 @@
         <v>-4.699999809265137</v>
       </c>
       <c r="D272">
-        <v>-1.511864185333252</v>
+        <v>-0.2864547967910767</v>
       </c>
     </row>
     <row r="273" spans="1:4">
@@ -4973,7 +4973,7 @@
         <v>5.199999809265137</v>
       </c>
       <c r="D273">
-        <v>4.87759256362915</v>
+        <v>3.338452816009521</v>
       </c>
     </row>
     <row r="274" spans="1:4">
@@ -4987,7 +4987,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D274">
-        <v>6.752933025360107</v>
+        <v>6.587450981140137</v>
       </c>
     </row>
     <row r="275" spans="1:4">
@@ -5001,7 +5001,7 @@
         <v>-3.599999904632568</v>
       </c>
       <c r="D275">
-        <v>-1.39143168926239</v>
+        <v>-1.648890733718872</v>
       </c>
     </row>
     <row r="276" spans="1:4">
@@ -5015,7 +5015,7 @@
         <v>0.6000000238418579</v>
       </c>
       <c r="D276">
-        <v>-3.577778339385986</v>
+        <v>-2.852264404296875</v>
       </c>
     </row>
     <row r="277" spans="1:4">
@@ -5029,7 +5029,7 @@
         <v>8.5</v>
       </c>
       <c r="D277">
-        <v>7.321761131286621</v>
+        <v>7.14592170715332</v>
       </c>
     </row>
     <row r="278" spans="1:4">
@@ -5043,7 +5043,7 @@
         <v>0.5</v>
       </c>
       <c r="D278">
-        <v>5.673820972442627</v>
+        <v>5.189748764038086</v>
       </c>
     </row>
     <row r="279" spans="1:4">
@@ -5057,7 +5057,7 @@
         <v>-5.699999809265137</v>
       </c>
       <c r="D279">
-        <v>-6.224160194396973</v>
+        <v>-5.763510704040527</v>
       </c>
     </row>
     <row r="280" spans="1:4">
@@ -5071,7 +5071,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D280">
-        <v>2.049452066421509</v>
+        <v>1.553286790847778</v>
       </c>
     </row>
     <row r="281" spans="1:4">
@@ -5085,7 +5085,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D281">
-        <v>2.906659603118896</v>
+        <v>3.101613283157349</v>
       </c>
     </row>
     <row r="282" spans="1:4">
@@ -5099,7 +5099,7 @@
         <v>-1.600000023841858</v>
       </c>
       <c r="D282">
-        <v>0.11255744099617</v>
+        <v>0.2603147923946381</v>
       </c>
     </row>
     <row r="283" spans="1:4">
@@ -5113,7 +5113,7 @@
         <v>8.399999618530273</v>
       </c>
       <c r="D283">
-        <v>3.929831027984619</v>
+        <v>3.442660331726074</v>
       </c>
     </row>
     <row r="284" spans="1:4">
@@ -5127,7 +5127,7 @@
         <v>35.70000076293945</v>
       </c>
       <c r="D284">
-        <v>27.79049110412598</v>
+        <v>26.09824562072754</v>
       </c>
     </row>
     <row r="285" spans="1:4">
@@ -5141,7 +5141,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D285">
-        <v>3.16152286529541</v>
+        <v>2.917777538299561</v>
       </c>
     </row>
     <row r="286" spans="1:4">
@@ -5155,7 +5155,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="D286">
-        <v>11.0490550994873</v>
+        <v>11.51745986938477</v>
       </c>
     </row>
     <row r="287" spans="1:4">
@@ -5169,7 +5169,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D287">
-        <v>-0.2797386646270752</v>
+        <v>-1.076552867889404</v>
       </c>
     </row>
     <row r="288" spans="1:4">
@@ -5183,7 +5183,7 @@
         <v>2</v>
       </c>
       <c r="D288">
-        <v>1.176302194595337</v>
+        <v>1.100629806518555</v>
       </c>
     </row>
     <row r="289" spans="1:4">
@@ -5197,7 +5197,7 @@
         <v>-0.5</v>
       </c>
       <c r="D289">
-        <v>-0.9108767509460449</v>
+        <v>0.1186195015907288</v>
       </c>
     </row>
     <row r="290" spans="1:4">
@@ -5211,7 +5211,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D290">
-        <v>-1.818617820739746</v>
+        <v>-1.371180534362793</v>
       </c>
     </row>
     <row r="291" spans="1:4">
@@ -5225,7 +5225,7 @@
         <v>-1.5</v>
       </c>
       <c r="D291">
-        <v>-1.009539604187012</v>
+        <v>-0.6945599913597107</v>
       </c>
     </row>
     <row r="292" spans="1:4">
@@ -5239,7 +5239,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D292">
-        <v>1.661227226257324</v>
+        <v>0.0455423891544342</v>
       </c>
     </row>
     <row r="293" spans="1:4">
@@ -5253,7 +5253,7 @@
         <v>2.700000047683716</v>
       </c>
       <c r="D293">
-        <v>1.379969358444214</v>
+        <v>0.7736376523971558</v>
       </c>
     </row>
     <row r="294" spans="1:4">
@@ -5267,7 +5267,7 @@
         <v>-1.200000047683716</v>
       </c>
       <c r="D294">
-        <v>1.354963660240173</v>
+        <v>-0.1218668818473816</v>
       </c>
     </row>
     <row r="295" spans="1:4">
@@ -5281,7 +5281,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D295">
-        <v>1.214565753936768</v>
+        <v>2.790791988372803</v>
       </c>
     </row>
     <row r="296" spans="1:4">
@@ -5295,7 +5295,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D296">
-        <v>1.098002433776855</v>
+        <v>0.9241302609443665</v>
       </c>
     </row>
     <row r="297" spans="1:4">
@@ -5309,7 +5309,7 @@
         <v>-15.69999980926514</v>
       </c>
       <c r="D297">
-        <v>-10.58336639404297</v>
+        <v>-10.52488613128662</v>
       </c>
     </row>
     <row r="298" spans="1:4">
@@ -5323,7 +5323,7 @@
         <v>12.80000019073486</v>
       </c>
       <c r="D298">
-        <v>5.310782909393311</v>
+        <v>5.724507331848145</v>
       </c>
     </row>
     <row r="299" spans="1:4">
@@ -5337,7 +5337,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D299">
-        <v>10.09700202941895</v>
+        <v>9.662148475646973</v>
       </c>
     </row>
     <row r="300" spans="1:4">
@@ -5351,7 +5351,7 @@
         <v>-1</v>
       </c>
       <c r="D300">
-        <v>-1.425455570220947</v>
+        <v>-2.40606164932251</v>
       </c>
     </row>
     <row r="301" spans="1:4">
@@ -5365,7 +5365,7 @@
         <v>11.10000038146973</v>
       </c>
       <c r="D301">
-        <v>7.28990650177002</v>
+        <v>6.209287643432617</v>
       </c>
     </row>
     <row r="302" spans="1:4">
@@ -5379,7 +5379,7 @@
         <v>3.700000047683716</v>
       </c>
       <c r="D302">
-        <v>-0.1241875886917114</v>
+        <v>-0.102095365524292</v>
       </c>
     </row>
     <row r="303" spans="1:4">
@@ -5393,7 +5393,7 @@
         <v>11</v>
       </c>
       <c r="D303">
-        <v>6.92503023147583</v>
+        <v>6.754134654998779</v>
       </c>
     </row>
     <row r="304" spans="1:4">
@@ -5407,7 +5407,7 @@
         <v>-4.599999904632568</v>
       </c>
       <c r="D304">
-        <v>-3.916982173919678</v>
+        <v>-3.457488298416138</v>
       </c>
     </row>
     <row r="305" spans="1:4">
@@ -5421,7 +5421,7 @@
         <v>-0.4000000059604645</v>
       </c>
       <c r="D305">
-        <v>0.5388400554656982</v>
+        <v>1.322627782821655</v>
       </c>
     </row>
     <row r="306" spans="1:4">
@@ -5435,7 +5435,7 @@
         <v>3.099999904632568</v>
       </c>
       <c r="D306">
-        <v>3.407827138900757</v>
+        <v>5.716917991638184</v>
       </c>
     </row>
     <row r="307" spans="1:4">
@@ -5449,7 +5449,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D307">
-        <v>-0.1330129504203796</v>
+        <v>-0.1534922122955322</v>
       </c>
     </row>
     <row r="308" spans="1:4">
@@ -5463,7 +5463,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D308">
-        <v>-1.501439809799194</v>
+        <v>-1.314213514328003</v>
       </c>
     </row>
     <row r="309" spans="1:4">
@@ -5477,7 +5477,7 @@
         <v>-1.5</v>
       </c>
       <c r="D309">
-        <v>-1.702250480651855</v>
+        <v>-2.187351226806641</v>
       </c>
     </row>
     <row r="310" spans="1:4">
@@ -5491,7 +5491,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D310">
-        <v>3.200104713439941</v>
+        <v>3.7027428150177</v>
       </c>
     </row>
     <row r="311" spans="1:4">
@@ -5505,7 +5505,7 @@
         <v>-3.799999952316284</v>
       </c>
       <c r="D311">
-        <v>-0.1754288673400879</v>
+        <v>-0.133958637714386</v>
       </c>
     </row>
     <row r="312" spans="1:4">
@@ -5519,7 +5519,7 @@
         <v>-1</v>
       </c>
       <c r="D312">
-        <v>-0.04417264461517334</v>
+        <v>0.2823168039321899</v>
       </c>
     </row>
     <row r="313" spans="1:4">
@@ -5533,7 +5533,7 @@
         <v>10</v>
       </c>
       <c r="D313">
-        <v>5.464127540588379</v>
+        <v>5.533763885498047</v>
       </c>
     </row>
     <row r="314" spans="1:4">
@@ -5547,7 +5547,7 @@
         <v>2.5</v>
       </c>
       <c r="D314">
-        <v>3.417068719863892</v>
+        <v>3.430106639862061</v>
       </c>
     </row>
     <row r="315" spans="1:4">
@@ -5561,7 +5561,7 @@
         <v>4.400000095367432</v>
       </c>
       <c r="D315">
-        <v>4.598618030548096</v>
+        <v>2.67975926399231</v>
       </c>
     </row>
     <row r="316" spans="1:4">
@@ -5575,7 +5575,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D316">
-        <v>-1.421135663986206</v>
+        <v>-0.4631965756416321</v>
       </c>
     </row>
     <row r="317" spans="1:4">
@@ -5589,7 +5589,7 @@
         <v>7.5</v>
       </c>
       <c r="D317">
-        <v>3.374427795410156</v>
+        <v>2.860108375549316</v>
       </c>
     </row>
     <row r="318" spans="1:4">
@@ -5603,7 +5603,7 @@
         <v>0.300000011920929</v>
       </c>
       <c r="D318">
-        <v>0.520500123500824</v>
+        <v>-0.4845295548439026</v>
       </c>
     </row>
     <row r="319" spans="1:4">
@@ -5617,7 +5617,7 @@
         <v>1.899999976158142</v>
       </c>
       <c r="D319">
-        <v>2.583849430084229</v>
+        <v>2.466715097427368</v>
       </c>
     </row>
     <row r="320" spans="1:4">
@@ -5631,7 +5631,7 @@
         <v>10.60000038146973</v>
       </c>
       <c r="D320">
-        <v>9.029491424560547</v>
+        <v>9.137580871582031</v>
       </c>
     </row>
     <row r="321" spans="1:4">
@@ -5645,7 +5645,7 @@
         <v>-5.300000190734863</v>
       </c>
       <c r="D321">
-        <v>-2.300573348999023</v>
+        <v>-1.612658500671387</v>
       </c>
     </row>
     <row r="322" spans="1:4">
@@ -5659,7 +5659,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D322">
-        <v>3.202980279922485</v>
+        <v>2.312020540237427</v>
       </c>
     </row>
     <row r="323" spans="1:4">
@@ -5673,7 +5673,7 @@
         <v>-4.099999904632568</v>
       </c>
       <c r="D323">
-        <v>-1.356188058853149</v>
+        <v>-1.85121488571167</v>
       </c>
     </row>
     <row r="324" spans="1:4">
@@ -5687,7 +5687,7 @@
         <v>2.299999952316284</v>
       </c>
       <c r="D324">
-        <v>1.371622920036316</v>
+        <v>1.512311697006226</v>
       </c>
     </row>
     <row r="325" spans="1:4">
@@ -5701,7 +5701,7 @@
         <v>7.5</v>
       </c>
       <c r="D325">
-        <v>6.337438583374023</v>
+        <v>4.716754913330078</v>
       </c>
     </row>
     <row r="326" spans="1:4">
@@ -5715,7 +5715,7 @@
         <v>-0.8999999761581421</v>
       </c>
       <c r="D326">
-        <v>-0.1013999581336975</v>
+        <v>-0.4137454032897949</v>
       </c>
     </row>
     <row r="327" spans="1:4">
@@ -5729,7 +5729,7 @@
         <v>-23.20000076293945</v>
       </c>
       <c r="D327">
-        <v>1.023591160774231</v>
+        <v>1.404204607009888</v>
       </c>
     </row>
     <row r="328" spans="1:4">
@@ -5743,7 +5743,7 @@
         <v>-1</v>
       </c>
       <c r="D328">
-        <v>0.2736423015594482</v>
+        <v>0.3668272793292999</v>
       </c>
     </row>
     <row r="329" spans="1:4">
@@ -5757,7 +5757,7 @@
         <v>-0.699999988079071</v>
       </c>
       <c r="D329">
-        <v>-0.8027911186218262</v>
+        <v>-1.538119792938232</v>
       </c>
     </row>
     <row r="330" spans="1:4">
@@ -5771,7 +5771,7 @@
         <v>-4.800000190734863</v>
       </c>
       <c r="D330">
-        <v>-7.662730693817139</v>
+        <v>-5.567154884338379</v>
       </c>
     </row>
     <row r="331" spans="1:4">
@@ -5785,7 +5785,7 @@
         <v>3.599999904632568</v>
       </c>
       <c r="D331">
-        <v>1.31596851348877</v>
+        <v>0.2647666335105896</v>
       </c>
     </row>
     <row r="332" spans="1:4">
@@ -5799,7 +5799,7 @@
         <v>4.900000095367432</v>
       </c>
       <c r="D332">
-        <v>2.424674987792969</v>
+        <v>1.220743775367737</v>
       </c>
     </row>
     <row r="333" spans="1:4">
@@ -5813,7 +5813,7 @@
         <v>11</v>
       </c>
       <c r="D333">
-        <v>3.172601699829102</v>
+        <v>3.016931533813477</v>
       </c>
     </row>
     <row r="334" spans="1:4">
@@ -5827,7 +5827,7 @@
         <v>-7.400000095367432</v>
       </c>
       <c r="D334">
-        <v>-8.902660369873047</v>
+        <v>-9.030138969421387</v>
       </c>
     </row>
     <row r="335" spans="1:4">
@@ -5841,7 +5841,7 @@
         <v>4.699999809265137</v>
       </c>
       <c r="D335">
-        <v>4.973186492919922</v>
+        <v>5.155522346496582</v>
       </c>
     </row>
     <row r="336" spans="1:4">
@@ -5855,7 +5855,7 @@
         <v>-1.700000047683716</v>
       </c>
       <c r="D336">
-        <v>0.2193572223186493</v>
+        <v>-0.1984684467315674</v>
       </c>
     </row>
     <row r="337" spans="1:4">
@@ -5869,7 +5869,7 @@
         <v>8.100000381469727</v>
       </c>
       <c r="D337">
-        <v>5.003509044647217</v>
+        <v>4.87835693359375</v>
       </c>
     </row>
     <row r="338" spans="1:4">
@@ -5883,7 +5883,7 @@
         <v>13.60000038146973</v>
       </c>
       <c r="D338">
-        <v>3.688033580780029</v>
+        <v>4.032439708709717</v>
       </c>
     </row>
     <row r="339" spans="1:4">
@@ -5897,7 +5897,7 @@
         <v>13.80000019073486</v>
       </c>
       <c r="D339">
-        <v>12.36788940429688</v>
+        <v>11.94052314758301</v>
       </c>
     </row>
     <row r="340" spans="1:4">
@@ -5911,7 +5911,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D340">
-        <v>-0.1893310546875</v>
+        <v>0.02150633931159973</v>
       </c>
     </row>
     <row r="341" spans="1:4">
@@ -5925,7 +5925,7 @@
         <v>4.300000190734863</v>
       </c>
       <c r="D341">
-        <v>0.8594163656234741</v>
+        <v>3.042312622070312</v>
       </c>
     </row>
     <row r="342" spans="1:4">
@@ -5939,7 +5939,7 @@
         <v>-4.099999904632568</v>
       </c>
       <c r="D342">
-        <v>-3.219497680664062</v>
+        <v>-3.246261358261108</v>
       </c>
     </row>
     <row r="343" spans="1:4">
@@ -5953,7 +5953,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="D343">
-        <v>0.1453945636749268</v>
+        <v>0.09312772750854492</v>
       </c>
     </row>
     <row r="344" spans="1:4">
@@ -5967,7 +5967,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D344">
-        <v>0.4631094932556152</v>
+        <v>-0.3079704642295837</v>
       </c>
     </row>
     <row r="345" spans="1:4">
@@ -5981,7 +5981,7 @@
         <v>7.300000190734863</v>
       </c>
       <c r="D345">
-        <v>7.457836627960205</v>
+        <v>6.711081981658936</v>
       </c>
     </row>
     <row r="346" spans="1:4">
@@ -5995,7 +5995,7 @@
         <v>2.599999904632568</v>
       </c>
       <c r="D346">
-        <v>5.053279399871826</v>
+        <v>5.401222229003906</v>
       </c>
     </row>
     <row r="347" spans="1:4">
@@ -6009,7 +6009,7 @@
         <v>-1.899999976158142</v>
       </c>
       <c r="D347">
-        <v>-4.394322872161865</v>
+        <v>-4.898582458496094</v>
       </c>
     </row>
     <row r="348" spans="1:4">
@@ -6023,7 +6023,7 @@
         <v>-2.400000095367432</v>
       </c>
       <c r="D348">
-        <v>5.14263391494751</v>
+        <v>4.982787132263184</v>
       </c>
     </row>
     <row r="349" spans="1:4">
@@ -6037,7 +6037,7 @@
         <v>-3.299999952316284</v>
       </c>
       <c r="D349">
-        <v>1.960752010345459</v>
+        <v>0.7271923422813416</v>
       </c>
     </row>
     <row r="350" spans="1:4">
@@ -6051,7 +6051,7 @@
         <v>1.700000047683716</v>
       </c>
       <c r="D350">
-        <v>3.987067699432373</v>
+        <v>4.090914726257324</v>
       </c>
     </row>
     <row r="351" spans="1:4">
@@ -6065,7 +6065,7 @@
         <v>-1.799999952316284</v>
       </c>
       <c r="D351">
-        <v>1.321181058883667</v>
+        <v>0.5981766581535339</v>
       </c>
     </row>
     <row r="352" spans="1:4">
@@ -6079,7 +6079,7 @@
         <v>7.099999904632568</v>
       </c>
       <c r="D352">
-        <v>1.261443138122559</v>
+        <v>0.2464537769556046</v>
       </c>
     </row>
     <row r="353" spans="1:4">
@@ -6093,7 +6093,7 @@
         <v>-2.200000047683716</v>
       </c>
       <c r="D353">
-        <v>-7.167930603027344</v>
+        <v>-7.69761848449707</v>
       </c>
     </row>
     <row r="354" spans="1:4">
@@ -6107,7 +6107,7 @@
         <v>-2.299999952316284</v>
       </c>
       <c r="D354">
-        <v>-0.4073097705841064</v>
+        <v>-0.5524522662162781</v>
       </c>
     </row>
     <row r="355" spans="1:4">
@@ -6121,7 +6121,7 @@
         <v>15.5</v>
       </c>
       <c r="D355">
-        <v>7.668662548065186</v>
+        <v>9.052423477172852</v>
       </c>
     </row>
     <row r="356" spans="1:4">
@@ -6135,7 +6135,7 @@
         <v>0.8999999761581421</v>
       </c>
       <c r="D356">
-        <v>-0.2390254735946655</v>
+        <v>0.09450754523277283</v>
       </c>
     </row>
     <row r="357" spans="1:4">
@@ -6149,7 +6149,7 @@
         <v>1.5</v>
       </c>
       <c r="D357">
-        <v>5.311734676361084</v>
+        <v>5.761501789093018</v>
       </c>
     </row>
     <row r="358" spans="1:4">
@@ -6163,7 +6163,7 @@
         <v>6.300000190734863</v>
       </c>
       <c r="D358">
-        <v>1.917190432548523</v>
+        <v>2.781132459640503</v>
       </c>
     </row>
     <row r="359" spans="1:4">
@@ -6177,7 +6177,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="D359">
-        <v>5.861521244049072</v>
+        <v>5.739429473876953</v>
       </c>
     </row>
     <row r="360" spans="1:4">
@@ -6191,7 +6191,7 @@
         <v>5.5</v>
       </c>
       <c r="D360">
-        <v>2.199129819869995</v>
+        <v>1.673351764678955</v>
       </c>
     </row>
     <row r="361" spans="1:4">
@@ -6205,7 +6205,7 @@
         <v>-1</v>
       </c>
       <c r="D361">
-        <v>0.9143397212028503</v>
+        <v>0.2696357667446136</v>
       </c>
     </row>
     <row r="362" spans="1:4">
@@ -6219,7 +6219,7 @@
         <v>5.900000095367432</v>
       </c>
       <c r="D362">
-        <v>-0.9579141139984131</v>
+        <v>-2.200068950653076</v>
       </c>
     </row>
     <row r="363" spans="1:4">
@@ -6233,7 +6233,7 @@
         <v>15.30000019073486</v>
       </c>
       <c r="D363">
-        <v>11.42156791687012</v>
+        <v>10.83066749572754</v>
       </c>
     </row>
     <row r="364" spans="1:4">
@@ -6247,7 +6247,7 @@
         <v>-3.099999904632568</v>
       </c>
       <c r="D364">
-        <v>-1.842439889907837</v>
+        <v>-2.915999412536621</v>
       </c>
     </row>
     <row r="365" spans="1:4">
@@ -6261,7 +6261,7 @@
         <v>1.5</v>
       </c>
       <c r="D365">
-        <v>1.28686511516571</v>
+        <v>0.9269905686378479</v>
       </c>
     </row>
     <row r="366" spans="1:4">
@@ -6275,7 +6275,7 @@
         <v>3.299999952316284</v>
       </c>
       <c r="D366">
-        <v>0.6476672291755676</v>
+        <v>0.7618557214736938</v>
       </c>
     </row>
     <row r="367" spans="1:4">
@@ -6289,7 +6289,7 @@
         <v>-5.699999809265137</v>
       </c>
       <c r="D367">
-        <v>-3.085970401763916</v>
+        <v>-3.062922239303589</v>
       </c>
     </row>
     <row r="368" spans="1:4">
@@ -6303,7 +6303,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="D368">
-        <v>10.96110343933105</v>
+        <v>10.59724426269531</v>
       </c>
     </row>
     <row r="369" spans="1:4">
@@ -6317,7 +6317,7 @@
         <v>-0.2000000029802322</v>
       </c>
       <c r="D369">
-        <v>0.8361556529998779</v>
+        <v>0.384946882724762</v>
       </c>
     </row>
   </sheetData>
